--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I637"/>
+  <dimension ref="A1:I638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21435,6 +21435,39 @@
       <c r="I637" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>359.18</v>
+      </c>
+      <c r="C638" t="n">
+        <v>369.51</v>
+      </c>
+      <c r="D638" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="E638" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="F638" t="n">
+        <v>369.74</v>
+      </c>
+      <c r="G638" t="n">
+        <v>361.88</v>
+      </c>
+      <c r="H638" t="n">
+        <v>357.16</v>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21449,7 +21482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B675"/>
+  <dimension ref="A1:B676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28202,6 +28235,16 @@
       </c>
       <c r="B675" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -28370,28 +28413,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2788385521764111</v>
+        <v>0.2726465214684506</v>
       </c>
       <c r="J2" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K2" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01471418878388253</v>
+        <v>0.0140963135940444</v>
       </c>
       <c r="M2" t="n">
-        <v>13.06932993845858</v>
+        <v>13.07820646350729</v>
       </c>
       <c r="N2" t="n">
-        <v>279.1732783669189</v>
+        <v>279.3197574669443</v>
       </c>
       <c r="O2" t="n">
-        <v>16.70847923561324</v>
+        <v>16.71286203697452</v>
       </c>
       <c r="P2" t="n">
-        <v>371.1924335993215</v>
+        <v>371.256992973608</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28452,28 +28495,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2143117959226868</v>
+        <v>0.2129416582479972</v>
       </c>
       <c r="J3" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K3" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04978534599034923</v>
+        <v>0.04931662843152429</v>
       </c>
       <c r="M3" t="n">
-        <v>4.67903560651957</v>
+        <v>4.678080349692958</v>
       </c>
       <c r="N3" t="n">
-        <v>47.23861344746907</v>
+        <v>47.19309952617424</v>
       </c>
       <c r="O3" t="n">
-        <v>6.873035242705297</v>
+        <v>6.869723395172053</v>
       </c>
       <c r="P3" t="n">
-        <v>368.1893592980287</v>
+        <v>368.2035855768774</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28534,28 +28577,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3687956571109958</v>
+        <v>0.365675189179719</v>
       </c>
       <c r="J4" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K4" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2110646815110114</v>
+        <v>0.2079201621986537</v>
       </c>
       <c r="M4" t="n">
-        <v>3.753141151420595</v>
+        <v>3.763243846633006</v>
       </c>
       <c r="N4" t="n">
-        <v>27.39568882449609</v>
+        <v>27.50287286820289</v>
       </c>
       <c r="O4" t="n">
-        <v>5.23408911124907</v>
+        <v>5.244318150932768</v>
       </c>
       <c r="P4" t="n">
-        <v>365.4727307482348</v>
+        <v>365.5051308841836</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28616,28 +28659,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3423945886063152</v>
+        <v>0.3395982162276415</v>
       </c>
       <c r="J5" t="n">
+        <v>637</v>
+      </c>
+      <c r="K5" t="n">
         <v>636</v>
       </c>
-      <c r="K5" t="n">
-        <v>635</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2102476434838223</v>
+        <v>0.2072766222326381</v>
       </c>
       <c r="M5" t="n">
-        <v>3.603947491009325</v>
+        <v>3.610247539747477</v>
       </c>
       <c r="N5" t="n">
-        <v>23.66552436589075</v>
+        <v>23.74862679733684</v>
       </c>
       <c r="O5" t="n">
-        <v>4.864722434619549</v>
+        <v>4.873256282747382</v>
       </c>
       <c r="P5" t="n">
-        <v>366.2650887066192</v>
+        <v>366.294148026387</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28698,28 +28741,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2865641630685581</v>
+        <v>0.2846843212280115</v>
       </c>
       <c r="J6" t="n">
+        <v>637</v>
+      </c>
+      <c r="K6" t="n">
         <v>636</v>
       </c>
-      <c r="K6" t="n">
-        <v>635</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.2647541876715516</v>
+        <v>0.2620180055019734</v>
       </c>
       <c r="M6" t="n">
-        <v>2.716093726493189</v>
+        <v>2.720495589118586</v>
       </c>
       <c r="N6" t="n">
-        <v>12.25564099387942</v>
+        <v>12.29074156684244</v>
       </c>
       <c r="O6" t="n">
-        <v>3.500805763517795</v>
+        <v>3.505815392578799</v>
       </c>
       <c r="P6" t="n">
-        <v>368.1105511556909</v>
+        <v>368.1300860808582</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -28780,28 +28823,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1867975493448957</v>
+        <v>-0.1876036842987032</v>
       </c>
       <c r="J7" t="n">
+        <v>637</v>
+      </c>
+      <c r="K7" t="n">
         <v>636</v>
       </c>
-      <c r="K7" t="n">
-        <v>635</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1229862613748209</v>
+        <v>0.1242165312718709</v>
       </c>
       <c r="M7" t="n">
-        <v>2.828633789991216</v>
+        <v>2.828061964931159</v>
       </c>
       <c r="N7" t="n">
-        <v>13.37194862074628</v>
+        <v>13.36092206612473</v>
       </c>
       <c r="O7" t="n">
-        <v>3.656767509802377</v>
+        <v>3.655259507357135</v>
       </c>
       <c r="P7" t="n">
-        <v>369.3089353826263</v>
+        <v>369.3173125692904</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -28862,28 +28905,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2133015350051259</v>
+        <v>-0.2145658504226459</v>
       </c>
       <c r="J8" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K8" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1658156255837043</v>
+        <v>0.167665678973118</v>
       </c>
       <c r="M8" t="n">
-        <v>2.580159929275375</v>
+        <v>2.582836366542829</v>
       </c>
       <c r="N8" t="n">
-        <v>12.28401027527707</v>
+        <v>12.28927306530297</v>
       </c>
       <c r="O8" t="n">
-        <v>3.50485524312732</v>
+        <v>3.505605948377964</v>
       </c>
       <c r="P8" t="n">
-        <v>366.7168426144636</v>
+        <v>366.7299864869766</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -28925,7 +28968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I637"/>
+  <dimension ref="A1:I638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58811,6 +58854,53 @@
         </is>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-36.62375167698257,174.77602147563712</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-36.62388284959726,174.775142998038</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-36.624011915316466,174.77427155000194</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-36.624282892419195,174.7734500658785</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-36.62465200534534,174.77269700808088</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-36.62504010031022,174.77194620677406</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>-36.62555598619205,174.77131878325295</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I638"/>
+  <dimension ref="A1:I639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21468,6 +21468,39 @@
       <c r="I638" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="C639" t="n">
+        <v>369.88</v>
+      </c>
+      <c r="D639" t="n">
+        <v>366.67</v>
+      </c>
+      <c r="E639" t="n">
+        <v>366.75</v>
+      </c>
+      <c r="F639" t="n">
+        <v>370</v>
+      </c>
+      <c r="G639" t="n">
+        <v>361.98</v>
+      </c>
+      <c r="H639" t="n">
+        <v>357.61</v>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21482,7 +21515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B676"/>
+  <dimension ref="A1:B677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28245,6 +28278,16 @@
       </c>
       <c r="B676" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>
@@ -28413,28 +28456,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2726465214684506</v>
+        <v>0.2693292408426372</v>
       </c>
       <c r="J2" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K2" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0140963135940444</v>
+        <v>0.0137993891794379</v>
       </c>
       <c r="M2" t="n">
-        <v>13.07820646350729</v>
+        <v>13.0733134550958</v>
       </c>
       <c r="N2" t="n">
-        <v>279.3197574669443</v>
+        <v>279.0474921660861</v>
       </c>
       <c r="O2" t="n">
-        <v>16.71286203697452</v>
+        <v>16.70471466880192</v>
       </c>
       <c r="P2" t="n">
-        <v>371.256992973608</v>
+        <v>371.2916412526663</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28495,28 +28538,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2129416582479972</v>
+        <v>0.211693842318443</v>
       </c>
       <c r="J3" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K3" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04931662843152429</v>
+        <v>0.04890695519633603</v>
       </c>
       <c r="M3" t="n">
-        <v>4.678080349692958</v>
+        <v>4.676532727765267</v>
       </c>
       <c r="N3" t="n">
-        <v>47.19309952617424</v>
+        <v>47.14285374736891</v>
       </c>
       <c r="O3" t="n">
-        <v>6.869723395172053</v>
+        <v>6.866065375990015</v>
       </c>
       <c r="P3" t="n">
-        <v>368.2035855768774</v>
+        <v>368.216564929787</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28577,28 +28620,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.365675189179719</v>
+        <v>0.3629874709433916</v>
       </c>
       <c r="J4" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K4" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2079201621986537</v>
+        <v>0.2054082478153118</v>
       </c>
       <c r="M4" t="n">
-        <v>3.763243846633006</v>
+        <v>3.771169074866892</v>
       </c>
       <c r="N4" t="n">
-        <v>27.50287286820289</v>
+        <v>27.57125164990019</v>
       </c>
       <c r="O4" t="n">
-        <v>5.244318150932768</v>
+        <v>5.250833424314677</v>
       </c>
       <c r="P4" t="n">
-        <v>365.5051308841836</v>
+        <v>365.5330876065534</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28659,28 +28702,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3395982162276415</v>
+        <v>0.3369001218383558</v>
       </c>
       <c r="J5" t="n">
+        <v>638</v>
+      </c>
+      <c r="K5" t="n">
         <v>637</v>
       </c>
-      <c r="K5" t="n">
-        <v>636</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2072766222326381</v>
+        <v>0.2044688333363743</v>
       </c>
       <c r="M5" t="n">
-        <v>3.610247539747477</v>
+        <v>3.616060167282313</v>
       </c>
       <c r="N5" t="n">
-        <v>23.74862679733684</v>
+        <v>23.8234673896136</v>
       </c>
       <c r="O5" t="n">
-        <v>4.873256282747382</v>
+        <v>4.880928947404746</v>
       </c>
       <c r="P5" t="n">
-        <v>366.294148026387</v>
+        <v>366.3222359106094</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28741,28 +28784,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2846843212280115</v>
+        <v>0.2828972073605513</v>
       </c>
       <c r="J6" t="n">
+        <v>638</v>
+      </c>
+      <c r="K6" t="n">
         <v>637</v>
       </c>
-      <c r="K6" t="n">
-        <v>636</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.2620180055019734</v>
+        <v>0.2594930951281181</v>
       </c>
       <c r="M6" t="n">
-        <v>2.720495589118586</v>
+        <v>2.724422820269523</v>
       </c>
       <c r="N6" t="n">
-        <v>12.29074156684244</v>
+        <v>12.32063756805306</v>
       </c>
       <c r="O6" t="n">
-        <v>3.505815392578799</v>
+        <v>3.510076575810428</v>
       </c>
       <c r="P6" t="n">
-        <v>368.1300860808582</v>
+        <v>368.1486904141984</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -28823,28 +28866,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1876036842987032</v>
+        <v>-0.1883692226902925</v>
       </c>
       <c r="J7" t="n">
+        <v>638</v>
+      </c>
+      <c r="K7" t="n">
         <v>637</v>
       </c>
-      <c r="K7" t="n">
-        <v>636</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1242165312718709</v>
+        <v>0.1254142706725629</v>
       </c>
       <c r="M7" t="n">
-        <v>2.828061964931159</v>
+        <v>2.827317762655311</v>
       </c>
       <c r="N7" t="n">
-        <v>13.36092206612473</v>
+        <v>13.34897366847052</v>
       </c>
       <c r="O7" t="n">
-        <v>3.655259507357135</v>
+        <v>3.653624730109883</v>
       </c>
       <c r="P7" t="n">
-        <v>369.3173125692904</v>
+        <v>369.3252820286971</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -28905,28 +28948,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2145658504226459</v>
+        <v>-0.2156754590412445</v>
       </c>
       <c r="J8" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K8" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L8" t="n">
-        <v>0.167665678973118</v>
+        <v>0.1693854600808848</v>
       </c>
       <c r="M8" t="n">
-        <v>2.582836366542829</v>
+        <v>2.584709772169683</v>
       </c>
       <c r="N8" t="n">
-        <v>12.28927306530297</v>
+        <v>12.28893810032472</v>
       </c>
       <c r="O8" t="n">
-        <v>3.505605948377964</v>
+        <v>3.505558172434843</v>
       </c>
       <c r="P8" t="n">
-        <v>366.7299864869766</v>
+        <v>366.7415424783489</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -28968,7 +29011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I638"/>
+  <dimension ref="A1:I639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58901,6 +58944,53 @@
         </is>
       </c>
     </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-36.62383143351664,174.7760281580828</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-36.623886142377415,174.7751436504983</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-36.62402312287789,174.77427615399674</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-36.62428507686164,174.77345139579802</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-36.62465393344339,174.77269865997997</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-36.625040741980015,174.77194699186924</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>-36.62555859961555,174.7713226306517</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I639"/>
+  <dimension ref="A1:I641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21501,6 +21501,72 @@
       <c r="I639" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>374.23</v>
+      </c>
+      <c r="C640" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="D640" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="E640" t="n">
+        <v>366.26</v>
+      </c>
+      <c r="F640" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="G640" t="n">
+        <v>362.03</v>
+      </c>
+      <c r="H640" t="n">
+        <v>357.29</v>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>374.23</v>
+      </c>
+      <c r="C641" t="n">
+        <v>369.82</v>
+      </c>
+      <c r="D641" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="E641" t="n">
+        <v>366.63</v>
+      </c>
+      <c r="F641" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="G641" t="n">
+        <v>362.72</v>
+      </c>
+      <c r="H641" t="n">
+        <v>357.76</v>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21515,7 +21581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B677"/>
+  <dimension ref="A1:B679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28288,6 +28354,26 @@
       </c>
       <c r="B677" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -28456,28 +28542,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2693292408426372</v>
+        <v>0.2666776038148864</v>
       </c>
       <c r="J2" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K2" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0137993891794379</v>
+        <v>0.01362420129838904</v>
       </c>
       <c r="M2" t="n">
-        <v>13.0733134550958</v>
+        <v>13.04462691875366</v>
       </c>
       <c r="N2" t="n">
-        <v>279.0474921660861</v>
+        <v>278.222476268039</v>
       </c>
       <c r="O2" t="n">
-        <v>16.70471466880192</v>
+        <v>16.68000228621204</v>
       </c>
       <c r="P2" t="n">
-        <v>371.2916412526663</v>
+        <v>371.3194301046356</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28538,28 +28624,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.211693842318443</v>
+        <v>0.2091406895041378</v>
       </c>
       <c r="J3" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K3" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04890695519633603</v>
+        <v>0.04806168676300304</v>
       </c>
       <c r="M3" t="n">
-        <v>4.676532727765267</v>
+        <v>4.673640609377333</v>
       </c>
       <c r="N3" t="n">
-        <v>47.14285374736891</v>
+        <v>47.04513085168094</v>
       </c>
       <c r="O3" t="n">
-        <v>6.866065375990015</v>
+        <v>6.8589453162772</v>
       </c>
       <c r="P3" t="n">
-        <v>368.216564929787</v>
+        <v>368.2432112899839</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28620,28 +28706,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3629874709433916</v>
+        <v>0.3596693882749538</v>
       </c>
       <c r="J4" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K4" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2054082478153118</v>
+        <v>0.2030604956649426</v>
       </c>
       <c r="M4" t="n">
-        <v>3.771169074866892</v>
+        <v>3.776299502193623</v>
       </c>
       <c r="N4" t="n">
-        <v>27.57125164990019</v>
+        <v>27.56986743995155</v>
       </c>
       <c r="O4" t="n">
-        <v>5.250833424314677</v>
+        <v>5.250701614065644</v>
       </c>
       <c r="P4" t="n">
-        <v>365.5330876065534</v>
+        <v>365.5677164879169</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28702,28 +28788,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3369001218383558</v>
+        <v>0.3313394367469661</v>
       </c>
       <c r="J5" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K5" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2044688333363743</v>
+        <v>0.1986395885759158</v>
       </c>
       <c r="M5" t="n">
-        <v>3.616060167282313</v>
+        <v>3.628264693103129</v>
       </c>
       <c r="N5" t="n">
-        <v>23.8234673896136</v>
+        <v>23.98663952363806</v>
       </c>
       <c r="O5" t="n">
-        <v>4.880928947404746</v>
+        <v>4.897615697830737</v>
       </c>
       <c r="P5" t="n">
-        <v>366.3222359106094</v>
+        <v>366.380317560437</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28784,28 +28870,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2828972073605513</v>
+        <v>0.2795631385491989</v>
       </c>
       <c r="J6" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K6" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2594930951281181</v>
+        <v>0.2549784135868297</v>
       </c>
       <c r="M6" t="n">
-        <v>2.724422820269523</v>
+        <v>2.731114681959649</v>
       </c>
       <c r="N6" t="n">
-        <v>12.32063756805306</v>
+        <v>12.36762558568033</v>
       </c>
       <c r="O6" t="n">
-        <v>3.510076575810428</v>
+        <v>3.516763510058691</v>
       </c>
       <c r="P6" t="n">
-        <v>368.1486904141984</v>
+        <v>368.1835146381468</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -28866,28 +28952,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1883692226902925</v>
+        <v>-0.1896270034303496</v>
       </c>
       <c r="J7" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K7" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1254142706725629</v>
+        <v>0.1275566626934331</v>
       </c>
       <c r="M7" t="n">
-        <v>2.827317762655311</v>
+        <v>2.824542873871439</v>
       </c>
       <c r="N7" t="n">
-        <v>13.34897366847052</v>
+        <v>13.3197329951877</v>
       </c>
       <c r="O7" t="n">
-        <v>3.653624730109883</v>
+        <v>3.649620938561661</v>
       </c>
       <c r="P7" t="n">
-        <v>369.3252820286971</v>
+        <v>369.3384185405205</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -28948,28 +29034,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2156754590412445</v>
+        <v>-0.2179180660801343</v>
       </c>
       <c r="J8" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K8" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1693854600808848</v>
+        <v>0.1728686211564165</v>
       </c>
       <c r="M8" t="n">
-        <v>2.584709772169683</v>
+        <v>2.588555235646055</v>
       </c>
       <c r="N8" t="n">
-        <v>12.28893810032472</v>
+        <v>12.28928685811933</v>
       </c>
       <c r="O8" t="n">
-        <v>3.505558172434843</v>
+        <v>3.505607915628804</v>
       </c>
       <c r="P8" t="n">
-        <v>366.7415424783489</v>
+        <v>366.7649753363264</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -29011,7 +29097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I639"/>
+  <dimension ref="A1:I641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58991,6 +59077,100 @@
         </is>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-36.62388700232964,174.776032813957</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-36.62388480746654,174.77514338598738</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-36.62404810461696,174.77428641634134</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-36.62428111250313,174.77344898224038</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-36.624655119965226,174.77269967653328</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-36.625041062814915,174.77194738441682</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>-36.625556741181065,174.77131989472366</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-36.62388700232964,174.776032813957</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-36.62388560841306,174.77514354469395</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-36.62405298118918,174.77428841960804</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-36.624284105998335,174.77345080472267</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-36.6246580121122,174.77270215438213</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-36.62504549033628,174.77195280157372</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>-36.62555947075669,174.771323913118</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I641"/>
+  <dimension ref="A1:I643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21544,7 +21544,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>374.23</v>
+        <v>374.2</v>
       </c>
       <c r="C641" t="n">
         <v>369.82</v>
@@ -21565,6 +21565,72 @@
         <v>357.76</v>
       </c>
       <c r="I641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:11:52+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>378.95</v>
+      </c>
+      <c r="C642" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="D642" t="n">
+        <v>371.05</v>
+      </c>
+      <c r="E642" t="n">
+        <v>366.62</v>
+      </c>
+      <c r="F642" t="n">
+        <v>369.56</v>
+      </c>
+      <c r="G642" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="H642" t="n">
+        <v>358.47</v>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>381.22</v>
+      </c>
+      <c r="C643" t="n">
+        <v>372.72</v>
+      </c>
+      <c r="D643" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="E643" t="n">
+        <v>367.19</v>
+      </c>
+      <c r="F643" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="G643" t="n">
+        <v>361.27</v>
+      </c>
+      <c r="H643" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="I643" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21581,7 +21647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B679"/>
+  <dimension ref="A1:B681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28374,6 +28440,26 @@
       </c>
       <c r="B679" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -28542,34 +28628,30 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2666776038148864</v>
+        <v>0.2677603164066372</v>
       </c>
       <c r="J2" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K2" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01362420129838904</v>
+        <v>0.01382863060038109</v>
       </c>
       <c r="M2" t="n">
-        <v>13.04462691875366</v>
+        <v>13.00929932298069</v>
       </c>
       <c r="N2" t="n">
-        <v>278.222476268039</v>
+        <v>277.3625077306415</v>
       </c>
       <c r="O2" t="n">
-        <v>16.68000228621204</v>
+        <v>16.65420390564021</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3194301046356</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>371.3080366319014</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.77575089246278 -36.6205220304128, 174.77644398980962 -36.628794074298945)</t>
@@ -28624,34 +28706,30 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2091406895041378</v>
+        <v>0.2081258775600667</v>
       </c>
       <c r="J3" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K3" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04806168676300304</v>
+        <v>0.04792988240350893</v>
       </c>
       <c r="M3" t="n">
-        <v>4.673640609377333</v>
+        <v>4.663701393950019</v>
       </c>
       <c r="N3" t="n">
-        <v>47.04513085168094</v>
+        <v>46.90676867843079</v>
       </c>
       <c r="O3" t="n">
-        <v>6.8589453162772</v>
+        <v>6.848851632093573</v>
       </c>
       <c r="P3" t="n">
-        <v>368.2432112899839</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>368.2538404293938</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.77449143235097 -36.62059442675695, 174.77611378442302 -36.628781780825534)</t>
@@ -28706,34 +28784,30 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3596693882749538</v>
+        <v>0.3576205944840578</v>
       </c>
       <c r="J4" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K4" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2030604956649426</v>
+        <v>0.2021487127330654</v>
       </c>
       <c r="M4" t="n">
-        <v>3.776299502193623</v>
+        <v>3.774947651895578</v>
       </c>
       <c r="N4" t="n">
-        <v>27.56986743995155</v>
+        <v>27.51799534311079</v>
       </c>
       <c r="O4" t="n">
-        <v>5.250701614065644</v>
+        <v>5.245759748893462</v>
       </c>
       <c r="P4" t="n">
-        <v>365.5677164879169</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>365.5891766061955</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.77298754674473 -36.620886108744905, 174.77622126850306 -36.628757814606494)</t>
@@ -28788,34 +28862,30 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3313394367469661</v>
+        <v>0.3261213084953539</v>
       </c>
       <c r="J5" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K5" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1986395885759158</v>
+        <v>0.1933698414264735</v>
       </c>
       <c r="M5" t="n">
-        <v>3.628264693103129</v>
+        <v>3.638858465577011</v>
       </c>
       <c r="N5" t="n">
-        <v>23.98663952363806</v>
+        <v>24.12158440540367</v>
       </c>
       <c r="O5" t="n">
-        <v>4.897615697830737</v>
+        <v>4.911372965414423</v>
       </c>
       <c r="P5" t="n">
-        <v>366.380317560437</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>366.4350242903137</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.7716449927784 -36.621317859606805, 174.77617773525844 -36.6287628879524)</t>
@@ -28870,34 +28940,30 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2795631385491989</v>
+        <v>0.275980778457559</v>
       </c>
       <c r="J6" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K6" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2549784135868297</v>
+        <v>0.2499274856107936</v>
       </c>
       <c r="M6" t="n">
-        <v>2.731114681959649</v>
+        <v>2.739148176009485</v>
       </c>
       <c r="N6" t="n">
-        <v>12.36762558568033</v>
+        <v>12.42821237723037</v>
       </c>
       <c r="O6" t="n">
-        <v>3.516763510058691</v>
+        <v>3.525366984759227</v>
       </c>
       <c r="P6" t="n">
-        <v>368.1835146381468</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>368.2210714254209</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.77034796489085 -36.621910075588104, 174.7761957523454 -36.628735466790836)</t>
@@ -28952,34 +29018,30 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1896270034303496</v>
+        <v>-0.1917852384040039</v>
       </c>
       <c r="J7" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K7" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1275566626934331</v>
+        <v>0.1305860051603792</v>
       </c>
       <c r="M7" t="n">
-        <v>2.824542873871439</v>
+        <v>2.826041318564178</v>
       </c>
       <c r="N7" t="n">
-        <v>13.3197329951877</v>
+        <v>13.3144155602224</v>
       </c>
       <c r="O7" t="n">
-        <v>3.649620938561661</v>
+        <v>3.648892374436713</v>
       </c>
       <c r="P7" t="n">
-        <v>369.3384185405205</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>369.3610445974027</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.76910518978553 -36.6227179890456, 174.77633311221447 -36.628625328986345)</t>
@@ -29034,34 +29096,30 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2179180660801343</v>
+        <v>-0.2191727573800003</v>
       </c>
       <c r="J8" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K8" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1728686211564165</v>
+        <v>0.1753795952000896</v>
       </c>
       <c r="M8" t="n">
-        <v>2.588555235646055</v>
+        <v>2.587125343198981</v>
       </c>
       <c r="N8" t="n">
-        <v>12.28928685811933</v>
+        <v>12.26406907128333</v>
       </c>
       <c r="O8" t="n">
-        <v>3.505607915628804</v>
+        <v>3.502009290576387</v>
       </c>
       <c r="P8" t="n">
-        <v>366.7649753363264</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>366.7781328698574</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.7682652270989 -36.623481699241616, 174.77613757918155 -36.62882900950516)</t>
@@ -29097,7 +29155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I641"/>
+  <dimension ref="A1:I643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59132,7 +59190,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>-36.62388700232964,174.776032813957</t>
+          <t>-36.62388673257812,174.77603279135565</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -59166,6 +59224,100 @@
         </is>
       </c>
       <c r="I641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:11:52+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-36.6239294432348,174.7760363699054</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-36.623901716337485,174.77514673646013</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-36.62406059548606,174.7742915475162</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-36.62428402509306,174.7734507554664</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-36.62465067050822,174.77269586445848</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-36.625031630268516,174.77193584351934</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>-36.62556359415786,174.77132998345897</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-36.623949854432645,174.7760380800772</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-36.62391141668968,174.77514865857415</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-36.624074198555505,174.77429713557854</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-36.624288636693734,174.77345356307447</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-36.62465608401422,174.77270050248288</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-36.62503618612441,174.77194141769397</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>-36.625570040601296,174.7713394737116</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I643"/>
+  <dimension ref="A1:I647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21633,6 +21633,138 @@
       <c r="I643" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>379.78</v>
+      </c>
+      <c r="C644" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="D644" t="n">
+        <v>372.13</v>
+      </c>
+      <c r="E644" t="n">
+        <v>366.81</v>
+      </c>
+      <c r="F644" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="G644" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="H644" t="n">
+        <v>359.28</v>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="C645" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="D645" t="n">
+        <v>374.55</v>
+      </c>
+      <c r="E645" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="F645" t="n">
+        <v>368.92</v>
+      </c>
+      <c r="G645" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="H645" t="n">
+        <v>359.59</v>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="C646" t="n">
+        <v>368.77</v>
+      </c>
+      <c r="D646" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="E646" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="F646" t="n">
+        <v>368.74</v>
+      </c>
+      <c r="G646" t="n">
+        <v>361.07</v>
+      </c>
+      <c r="H646" t="n">
+        <v>359.14</v>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>379.67</v>
+      </c>
+      <c r="C647" t="n">
+        <v>371.87</v>
+      </c>
+      <c r="D647" t="n">
+        <v>375.27</v>
+      </c>
+      <c r="E647" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="F647" t="n">
+        <v>370.47</v>
+      </c>
+      <c r="G647" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="H647" t="n">
+        <v>359.6</v>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21647,7 +21779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B681"/>
+  <dimension ref="A1:B685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28460,6 +28592,46 @@
       </c>
       <c r="B681" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -28628,28 +28800,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2677603164066372</v>
+        <v>0.2687311169804692</v>
       </c>
       <c r="J2" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K2" t="n">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01382863060038109</v>
+        <v>0.01412104092913113</v>
       </c>
       <c r="M2" t="n">
-        <v>13.00929932298069</v>
+        <v>12.93422157460959</v>
       </c>
       <c r="N2" t="n">
-        <v>277.3625077306415</v>
+        <v>275.6383297322377</v>
       </c>
       <c r="O2" t="n">
-        <v>16.65420390564021</v>
+        <v>16.6023591616444</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3080366319014</v>
+        <v>371.2977959179186</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28706,28 +28878,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2081258775600667</v>
+        <v>0.2028107693384754</v>
       </c>
       <c r="J3" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K3" t="n">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04792988240350893</v>
+        <v>0.04612088590407359</v>
       </c>
       <c r="M3" t="n">
-        <v>4.663701393950019</v>
+        <v>4.65897028612825</v>
       </c>
       <c r="N3" t="n">
-        <v>46.90676867843079</v>
+        <v>46.73696019017047</v>
       </c>
       <c r="O3" t="n">
-        <v>6.848851632093573</v>
+        <v>6.836443533751337</v>
       </c>
       <c r="P3" t="n">
-        <v>368.2538404293938</v>
+        <v>368.3096828892022</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28784,28 +28956,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3576205944840578</v>
+        <v>0.3561663602208793</v>
       </c>
       <c r="J4" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K4" t="n">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2021487127330654</v>
+        <v>0.202992471860851</v>
       </c>
       <c r="M4" t="n">
-        <v>3.774947651895578</v>
+        <v>3.759452876657825</v>
       </c>
       <c r="N4" t="n">
-        <v>27.51799534311079</v>
+        <v>27.36346091974121</v>
       </c>
       <c r="O4" t="n">
-        <v>5.245759748893462</v>
+        <v>5.231009550721659</v>
       </c>
       <c r="P4" t="n">
-        <v>365.5891766061955</v>
+        <v>365.6044433413743</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28862,28 +29034,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3261213084953539</v>
+        <v>0.31775541964522</v>
       </c>
       <c r="J5" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K5" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1933698414264735</v>
+        <v>0.1857444403944269</v>
       </c>
       <c r="M5" t="n">
-        <v>3.638858465577011</v>
+        <v>3.651453075748813</v>
       </c>
       <c r="N5" t="n">
-        <v>24.12158440540367</v>
+        <v>24.25324890172911</v>
       </c>
       <c r="O5" t="n">
-        <v>4.911372965414423</v>
+        <v>4.924758765841136</v>
       </c>
       <c r="P5" t="n">
-        <v>366.4350242903137</v>
+        <v>366.5230002911778</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28940,28 +29112,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.275980778457559</v>
+        <v>0.2678957259175019</v>
       </c>
       <c r="J6" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K6" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2499274856107936</v>
+        <v>0.2377240859261771</v>
       </c>
       <c r="M6" t="n">
-        <v>2.739148176009485</v>
+        <v>2.760375795639351</v>
       </c>
       <c r="N6" t="n">
-        <v>12.42821237723037</v>
+        <v>12.60984250722215</v>
       </c>
       <c r="O6" t="n">
-        <v>3.525366984759227</v>
+        <v>3.551034005359868</v>
       </c>
       <c r="P6" t="n">
-        <v>368.2210714254209</v>
+        <v>368.3060971030594</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29018,28 +29190,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1917852384040039</v>
+        <v>-0.1947426847863992</v>
       </c>
       <c r="J7" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K7" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1305860051603792</v>
+        <v>0.1353839903274145</v>
       </c>
       <c r="M7" t="n">
-        <v>2.826041318564178</v>
+        <v>2.822473844997783</v>
       </c>
       <c r="N7" t="n">
-        <v>13.3144155602224</v>
+        <v>13.27141867414782</v>
       </c>
       <c r="O7" t="n">
-        <v>3.648892374436713</v>
+        <v>3.642995837788979</v>
       </c>
       <c r="P7" t="n">
-        <v>369.3610445974027</v>
+        <v>369.3921399102735</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29096,28 +29268,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2191727573800003</v>
+        <v>-0.2211255629833843</v>
       </c>
       <c r="J8" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K8" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1753795952000896</v>
+        <v>0.1798362152301543</v>
       </c>
       <c r="M8" t="n">
-        <v>2.587125343198981</v>
+        <v>2.581376211567708</v>
       </c>
       <c r="N8" t="n">
-        <v>12.26406907128333</v>
+        <v>12.20317285911234</v>
       </c>
       <c r="O8" t="n">
-        <v>3.502009290576387</v>
+        <v>3.49330400324855</v>
       </c>
       <c r="P8" t="n">
-        <v>366.7781328698574</v>
+        <v>366.7986796249571</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29155,7 +29327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I643"/>
+  <dimension ref="A1:I647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59323,6 +59495,194 @@
         </is>
       </c>
     </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-36.623936906360015,174.77603699521038</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-36.623878132912175,174.7751420634328</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-36.62406983530684,174.77429534318097</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-36.6242855622933,174.7734516913357</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-36.62464036259898,174.77268703315363</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-36.62503746946404,174.7719429878841</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>-36.625568298319365,174.7713369087783</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-36.62393205083277,174.77603658838544</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-36.62387350522113,174.77514114646175</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-36.624090539349154,174.774303848285</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-36.624302147874225,174.7734617888756</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-36.62464592442061,174.7726917982459</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-36.62503823946782,174.77194392999823</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>-36.62557009867735,174.77133955920937</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-36.62392135068935,174.77603569186402</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-36.623876264036944,174.77514169311755</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-36.62408318171438,174.77430082580946</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-36.62429373372598,174.77345666622065</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-36.62464458958345,174.77269065462366</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-36.62503490278475,174.77193984750386</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>-36.62556748525443,174.77133571180946</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-36.62393591727113,174.7760369123386</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-36.62390385219485,174.77514715967783</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-36.62409669922937,174.77430637873013</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-36.62431193741174,174.77346774888903</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-36.624657418851285,174.77270164610542</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-36.625050495360114,174.7719589253171</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-36.62557015675342,174.77133964470715</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I647"/>
+  <dimension ref="A1:I654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21763,6 +21763,237 @@
         <v>359.6</v>
       </c>
       <c r="I647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>378.13</v>
+      </c>
+      <c r="C648" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="D648" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="E648" t="n">
+        <v>370.15</v>
+      </c>
+      <c r="F648" t="n">
+        <v>370.66</v>
+      </c>
+      <c r="G648" t="n">
+        <v>363.74</v>
+      </c>
+      <c r="H648" t="n">
+        <v>360.32</v>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>374.78</v>
+      </c>
+      <c r="C649" t="n">
+        <v>367.06</v>
+      </c>
+      <c r="D649" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="E649" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="F649" t="n">
+        <v>369.93</v>
+      </c>
+      <c r="G649" t="n">
+        <v>363.01</v>
+      </c>
+      <c r="H649" t="n">
+        <v>359.91</v>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="C650" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="D650" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="E650" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="F650" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="G650" t="n">
+        <v>362.96</v>
+      </c>
+      <c r="H650" t="n">
+        <v>359.63</v>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>369.26</v>
+      </c>
+      <c r="C651" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="D651" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="E651" t="n">
+        <v>368.08</v>
+      </c>
+      <c r="F651" t="n">
+        <v>369.09</v>
+      </c>
+      <c r="G651" t="n">
+        <v>362.42</v>
+      </c>
+      <c r="H651" t="n">
+        <v>359.53</v>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="C652" t="n">
+        <v>364.22</v>
+      </c>
+      <c r="D652" t="n">
+        <v>372.63</v>
+      </c>
+      <c r="E652" t="n">
+        <v>367.51</v>
+      </c>
+      <c r="F652" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="G652" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="H652" t="n">
+        <v>359.12</v>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>366.2</v>
+      </c>
+      <c r="C653" t="n">
+        <v>364.44</v>
+      </c>
+      <c r="D653" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="E653" t="n">
+        <v>367.52</v>
+      </c>
+      <c r="F653" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="G653" t="n">
+        <v>362.41</v>
+      </c>
+      <c r="H653" t="n">
+        <v>359.4</v>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="C654" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="D654" t="n">
+        <v>371.79</v>
+      </c>
+      <c r="E654" t="n">
+        <v>367.51</v>
+      </c>
+      <c r="F654" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="G654" t="n">
+        <v>362.06</v>
+      </c>
+      <c r="H654" t="n">
+        <v>360.23</v>
+      </c>
+      <c r="I654" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21779,7 +22010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B685"/>
+  <dimension ref="A1:B692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28632,6 +28863,76 @@
       </c>
       <c r="B685" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -28800,28 +29101,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2687311169804692</v>
+        <v>0.2510812438138997</v>
       </c>
       <c r="J2" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K2" t="n">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01412104092913113</v>
+        <v>0.0126087229058891</v>
       </c>
       <c r="M2" t="n">
-        <v>12.93422157460959</v>
+        <v>12.87814899326577</v>
       </c>
       <c r="N2" t="n">
-        <v>275.6383297322377</v>
+        <v>273.5723865931663</v>
       </c>
       <c r="O2" t="n">
-        <v>16.6023591616444</v>
+        <v>16.54002377849459</v>
       </c>
       <c r="P2" t="n">
-        <v>371.2977959179186</v>
+        <v>371.4855583725177</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28878,28 +29179,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2028107693384754</v>
+        <v>0.1865267216814555</v>
       </c>
       <c r="J3" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K3" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04612088590407359</v>
+        <v>0.03970717125084633</v>
       </c>
       <c r="M3" t="n">
-        <v>4.65897028612825</v>
+        <v>4.682640577862935</v>
       </c>
       <c r="N3" t="n">
-        <v>46.73696019017047</v>
+        <v>46.85686966053893</v>
       </c>
       <c r="O3" t="n">
-        <v>6.836443533751337</v>
+        <v>6.845207787973929</v>
       </c>
       <c r="P3" t="n">
-        <v>368.3096828892022</v>
+        <v>368.482118992264</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28956,28 +29257,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3561663602208793</v>
+        <v>0.3523518115674569</v>
       </c>
       <c r="J4" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K4" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="L4" t="n">
-        <v>0.202992471860851</v>
+        <v>0.2031602114240817</v>
       </c>
       <c r="M4" t="n">
-        <v>3.759452876657825</v>
+        <v>3.739199248555815</v>
       </c>
       <c r="N4" t="n">
-        <v>27.36346091974121</v>
+        <v>27.11700948762726</v>
       </c>
       <c r="O4" t="n">
-        <v>5.231009550721659</v>
+        <v>5.207399493761474</v>
       </c>
       <c r="P4" t="n">
-        <v>365.6044433413743</v>
+        <v>365.6448638199359</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29034,28 +29335,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.31775541964522</v>
+        <v>0.3034752084006579</v>
       </c>
       <c r="J5" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K5" t="n">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1857444403944269</v>
+        <v>0.172956870274009</v>
       </c>
       <c r="M5" t="n">
-        <v>3.651453075748813</v>
+        <v>3.671295686579558</v>
       </c>
       <c r="N5" t="n">
-        <v>24.25324890172911</v>
+        <v>24.46111069404306</v>
       </c>
       <c r="O5" t="n">
-        <v>4.924758765841136</v>
+        <v>4.945817495019712</v>
       </c>
       <c r="P5" t="n">
-        <v>366.5230002911778</v>
+        <v>366.6743333891666</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29112,28 +29413,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2678957259175019</v>
+        <v>0.2547975499665388</v>
       </c>
       <c r="J6" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K6" t="n">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2377240859261771</v>
+        <v>0.2189306197150948</v>
       </c>
       <c r="M6" t="n">
-        <v>2.760375795639351</v>
+        <v>2.793670230389456</v>
       </c>
       <c r="N6" t="n">
-        <v>12.60984250722215</v>
+        <v>12.86509500483956</v>
       </c>
       <c r="O6" t="n">
-        <v>3.551034005359868</v>
+        <v>3.58679453061359</v>
       </c>
       <c r="P6" t="n">
-        <v>368.3060971030594</v>
+        <v>368.4448977387117</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29190,28 +29491,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1947426847863992</v>
+        <v>-0.1978874809720068</v>
       </c>
       <c r="J7" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K7" t="n">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1353839903274145</v>
+        <v>0.1418932636327651</v>
       </c>
       <c r="M7" t="n">
-        <v>2.822473844997783</v>
+        <v>2.806825913673938</v>
       </c>
       <c r="N7" t="n">
-        <v>13.27141867414782</v>
+        <v>13.15393131116463</v>
       </c>
       <c r="O7" t="n">
-        <v>3.642995837788979</v>
+        <v>3.626834888875509</v>
       </c>
       <c r="P7" t="n">
-        <v>369.3921399102735</v>
+        <v>369.4254746640993</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29268,28 +29569,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2211255629833843</v>
+        <v>-0.2236192138836416</v>
       </c>
       <c r="J8" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K8" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1798362152301543</v>
+        <v>0.1866484923223579</v>
       </c>
       <c r="M8" t="n">
-        <v>2.581376211567708</v>
+        <v>2.566571241874605</v>
       </c>
       <c r="N8" t="n">
-        <v>12.20317285911234</v>
+        <v>12.08807286322733</v>
       </c>
       <c r="O8" t="n">
-        <v>3.49330400324855</v>
+        <v>3.476790598127435</v>
       </c>
       <c r="P8" t="n">
-        <v>366.7986796249571</v>
+        <v>366.8251144822112</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29327,7 +29628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I647"/>
+  <dimension ref="A1:I654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59683,6 +59984,335 @@
         </is>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-36.62392207002673,174.77603575213436</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-36.6238757300726,174.77514158731321</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-36.624098153645505,174.77430697619639</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-36.62431258465388,174.77346814293958</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-36.624658827845955,174.77270285326262</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-36.62505203536737,174.771960809546</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-36.62557433822981,174.77134580054758</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-36.623891947774126,174.77603322831516</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-36.623861046052866,174.77513867769423</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-36.62408917048688,174.77430328596392</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-36.624304898653385,174.77346346358996</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-36.62465341434005,174.7726982152379</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-36.62504735117851,174.77195507835003</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-36.62557195711135,174.77134229513837</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-36.623863623864736,174.77603085517396</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-36.62385187966472,174.77513686138724</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-36.62408112842093,174.77429998232802</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-36.624299316189735,174.77346006490507</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-36.624649483986325,174.7726948479053</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>-36.625047030343644,174.77195468580237</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>-36.6255703309816,174.7713399012005</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-36.62384231349468,174.77602906966916</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-36.62384538309834,174.77513557410197</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-36.62408189840598,174.77430029863356</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-36.62429583726306,174.7734579468843</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-36.62464718510015,174.77269287833357</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>-36.62504356532702,174.77195044628806</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>-36.625569750220976,174.77133904622272</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-36.6238205535386,174.77602724649674</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-36.62383577173982,174.7751336696256</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-36.62407411300162,174.77429710043347</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-36.62429122566251,174.77345513927565</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-36.62464533115964,174.77269128996934</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>-36.625044078662825,174.7719510743642</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>-36.62556736910231,174.7713355408139</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-36.62381479883945,174.77602676433565</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-36.62383772960914,174.77513405757443</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-36.62407000641464,174.77429541347107</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-36.624291306567784,174.77345518853195</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-36.624644441268195,174.77269052755454</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>-36.62504350116004,174.77195036777852</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>-36.62556899523215,174.77133793475159</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-36.62380625670788,174.77602604862795</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-36.6238622919697,174.77513892457094</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-36.62406692647439,174.77429414824937</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-36.62429122566251,174.77345513927565</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-36.62464540531727,174.77269135350392</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>-36.62504125531585,174.77194761994537</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>-36.625573815545266,174.77134503106748</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I654"/>
+  <dimension ref="A1:I658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21973,7 +21973,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>365.25</v>
+        <v>368.85</v>
       </c>
       <c r="C654" t="n">
         <v>367.2</v>
@@ -21994,6 +21994,138 @@
         <v>360.23</v>
       </c>
       <c r="I654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="C655" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="D655" t="n">
+        <v>371.71</v>
+      </c>
+      <c r="E655" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="F655" t="n">
+        <v>368.34</v>
+      </c>
+      <c r="G655" t="n">
+        <v>361.42</v>
+      </c>
+      <c r="H655" t="n">
+        <v>359.48</v>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="C656" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="D656" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="E656" t="n">
+        <v>369.7</v>
+      </c>
+      <c r="F656" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="G656" t="n">
+        <v>361.12</v>
+      </c>
+      <c r="H656" t="n">
+        <v>360.67</v>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="C657" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="D657" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="E657" t="n">
+        <v>369.7</v>
+      </c>
+      <c r="F657" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="G657" t="n">
+        <v>361.12</v>
+      </c>
+      <c r="H657" t="n">
+        <v>360.67</v>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="C658" t="n">
+        <v>371.16</v>
+      </c>
+      <c r="D658" t="n">
+        <v>372.91</v>
+      </c>
+      <c r="E658" t="n">
+        <v>369.33</v>
+      </c>
+      <c r="F658" t="n">
+        <v>368.27</v>
+      </c>
+      <c r="G658" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="H658" t="n">
+        <v>360.19</v>
+      </c>
+      <c r="I658" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22010,7 +22142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B692"/>
+  <dimension ref="A1:B696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28933,6 +29065,46 @@
       </c>
       <c r="B692" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>-0.88</v>
       </c>
     </row>
   </sheetData>
@@ -29101,28 +29273,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2510812438138997</v>
+        <v>0.2447341457308741</v>
       </c>
       <c r="J2" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K2" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0126087229058891</v>
+        <v>0.01214316676532678</v>
       </c>
       <c r="M2" t="n">
-        <v>12.87814899326577</v>
+        <v>12.8289870877056</v>
       </c>
       <c r="N2" t="n">
-        <v>273.5723865931663</v>
+        <v>272.0536817104854</v>
       </c>
       <c r="O2" t="n">
-        <v>16.54002377849459</v>
+        <v>16.49404988808041</v>
       </c>
       <c r="P2" t="n">
-        <v>371.4855583725177</v>
+        <v>371.5533342193709</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29179,28 +29351,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1865267216814555</v>
+        <v>0.1828270820073578</v>
       </c>
       <c r="J3" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K3" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03970717125084633</v>
+        <v>0.0386618281333827</v>
       </c>
       <c r="M3" t="n">
-        <v>4.682640577862935</v>
+        <v>4.671127267792935</v>
       </c>
       <c r="N3" t="n">
-        <v>46.85686966053893</v>
+        <v>46.63441379755098</v>
       </c>
       <c r="O3" t="n">
-        <v>6.845207787973929</v>
+        <v>6.828939434315623</v>
       </c>
       <c r="P3" t="n">
-        <v>368.482118992264</v>
+        <v>368.5214555420799</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29257,28 +29429,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3523518115674569</v>
+        <v>0.3498848281935668</v>
       </c>
       <c r="J4" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K4" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2031602114240817</v>
+        <v>0.2029237013274581</v>
       </c>
       <c r="M4" t="n">
-        <v>3.739199248555815</v>
+        <v>3.728641518044001</v>
       </c>
       <c r="N4" t="n">
-        <v>27.11700948762726</v>
+        <v>26.98043870262778</v>
       </c>
       <c r="O4" t="n">
-        <v>5.207399493761474</v>
+        <v>5.194269794940169</v>
       </c>
       <c r="P4" t="n">
-        <v>365.6448638199359</v>
+        <v>365.6710971381843</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29335,28 +29507,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3034752084006579</v>
+        <v>0.2963623640289751</v>
       </c>
       <c r="J5" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K5" t="n">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="L5" t="n">
-        <v>0.172956870274009</v>
+        <v>0.1669672567865887</v>
       </c>
       <c r="M5" t="n">
-        <v>3.671295686579558</v>
+        <v>3.678538196722799</v>
       </c>
       <c r="N5" t="n">
-        <v>24.46111069404306</v>
+        <v>24.52486076203425</v>
       </c>
       <c r="O5" t="n">
-        <v>4.945817495019712</v>
+        <v>4.952258147757874</v>
       </c>
       <c r="P5" t="n">
-        <v>366.6743333891666</v>
+        <v>366.7500233401398</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29413,28 +29585,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2547975499665388</v>
+        <v>0.2465929274386706</v>
       </c>
       <c r="J6" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K6" t="n">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2189306197150948</v>
+        <v>0.2067146629772478</v>
       </c>
       <c r="M6" t="n">
-        <v>2.793670230389456</v>
+        <v>2.816970012376199</v>
       </c>
       <c r="N6" t="n">
-        <v>12.86509500483956</v>
+        <v>13.06017707536718</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58679453061359</v>
+        <v>3.613886699298579</v>
       </c>
       <c r="P6" t="n">
-        <v>368.4448977387117</v>
+        <v>368.5322122691927</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29491,28 +29663,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1978874809720068</v>
+        <v>-0.2016464092459582</v>
       </c>
       <c r="J7" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K7" t="n">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1418932636327651</v>
+        <v>0.1476992834892146</v>
       </c>
       <c r="M7" t="n">
-        <v>2.806825913673938</v>
+        <v>2.807340298205677</v>
       </c>
       <c r="N7" t="n">
-        <v>13.15393131116463</v>
+        <v>13.13182662039859</v>
       </c>
       <c r="O7" t="n">
-        <v>3.626834888875509</v>
+        <v>3.623786227193677</v>
       </c>
       <c r="P7" t="n">
-        <v>369.4254746640993</v>
+        <v>369.4654805413487</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29569,28 +29741,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2236192138836416</v>
+        <v>-0.2243255277952201</v>
       </c>
       <c r="J8" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K8" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1866484923223579</v>
+        <v>0.1896605288202168</v>
       </c>
       <c r="M8" t="n">
-        <v>2.566571241874605</v>
+        <v>2.554562454061027</v>
       </c>
       <c r="N8" t="n">
-        <v>12.08807286322733</v>
+        <v>12.01794717583618</v>
       </c>
       <c r="O8" t="n">
-        <v>3.476790598127435</v>
+        <v>3.46669109899284</v>
       </c>
       <c r="P8" t="n">
-        <v>366.8251144822112</v>
+        <v>366.8326326462919</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29628,7 +29800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I654"/>
+  <dimension ref="A1:I658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60274,7 +60446,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>-36.62380625670788,174.77602604862795</t>
+          <t>-36.62383862689055,174.7760287607845</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -60308,6 +60480,194 @@
         </is>
       </c>
       <c r="I654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-36.62382837633273,174.7760279019346</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-36.62387306025083,174.7751410582915</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-36.62406624204323,174.77429386708903</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-36.624287423114616,174.77345282423022</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-36.624641623278556,174.77268811324114</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>-36.62503714862913,174.77194259533658</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>-36.62556945984065,174.77133861873384</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-36.62385598090502,174.77603021480292</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-36.62389682166433,174.77514576658626</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-36.6240841228072,174.77430121240516</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>-36.62430894391683,174.77346592640544</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>-36.624644441268195,174.77269052755454</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>-36.62503522361966,174.77194024005138</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>-36.62557637089181,174.77134879297023</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-36.6238936562004,174.77603337145706</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-36.62389682166433,174.77514576658626</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-36.6240841228072,174.77430121240516</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-36.62430894391683,174.77346592640544</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>-36.624644441268195,174.77269052755454</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>-36.62503522361966,174.77194024005138</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>-36.62557637089181,174.77134879297023</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-36.6238936562004,174.77603337145706</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-36.623897533616784,174.7751459076588</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-36.62407650851066,174.77429808449497</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-36.6243059504219,174.77346410392195</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-36.624641104175204,174.77268766849923</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>-36.62503086026466,174.7719349014054</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>-36.62557358324105,174.77134468907633</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
